--- a/event_registration_forms/006_stem_summer_camp_enrollment_form--event_registration_forms.xlsx
+++ b/event_registration_forms/006_stem_summer_camp_enrollment_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
+          <t>medical_conditions_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Medical Conditions</t>
+          <t>Medical Conditions 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>session_dates</t>
+          <t>session_dates_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Session Dates</t>
+          <t>Session Dates 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>payment_terms</t>
+          <t>payment_terms_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Payment Terms</t>
+          <t>Payment Terms 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>medical_info</t>
+          <t>medical_info_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Medical Information</t>
+          <t>Medical Info 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Medical Information</t>
+          <t>Camper Medical Info</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Medical Information</t>
+          <t>Camper Medical</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>camper_fee</t>
+          <t>camper_fee_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Camper Fee</t>
+          <t>Camper Fee 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>payment_method_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Payment Method</t>
+          <t>Payment Method 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>medical_conditions_choices</t>
+          <t>medical_conditions_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>medical_conditions_choices</t>
+          <t>medical_conditions_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>session_dates_choices</t>
+          <t>session_dates_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>session_dates_choices</t>
+          <t>session_dates_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>session_dates_choices</t>
+          <t>session_dates_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
